--- a/Longevity/Transcriptomics/Wilson_2013/1-s2.0-S0047637412001832-mmc4.xlsx
+++ b/Longevity/Transcriptomics/Wilson_2013/1-s2.0-S0047637412001832-mmc4.xlsx
@@ -12515,7 +12515,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -12640,20 +12640,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -12850,6 +12838,10 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15436,7 +15428,7 @@
       <c r="A18" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="16" t="s">
         <v>1138</v>
       </c>
       <c r="C18" s="25" t="s">
@@ -15812,7 +15804,7 @@
       <c r="A24" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="16" t="s">
         <v>2774</v>
       </c>
       <c r="C24" s="25" t="s">
@@ -16314,7 +16306,7 @@
       <c r="A32" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="16" t="s">
         <v>1556</v>
       </c>
       <c r="C32" s="25" t="s">
@@ -16376,7 +16368,7 @@
       <c r="X32" s="38"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>585</v>
       </c>
@@ -16500,7 +16492,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>231</v>
       </c>
@@ -16562,11 +16554,11 @@
         <v>768</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>696</v>
       </c>
-      <c r="B36" s="44" t="s">
+      <c r="B36" s="16" t="s">
         <v>3030</v>
       </c>
       <c r="C36" s="25" t="s">
@@ -16611,7 +16603,7 @@
       <c r="P36" s="12" t="s">
         <v>3031</v>
       </c>
-      <c r="Q36" s="48" t="s">
+      <c r="Q36" s="18" t="s">
         <v>3032</v>
       </c>
       <c r="R36" s="13" t="s">
@@ -16753,7 +16745,7 @@
       <c r="X38" s="38"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" ht="72" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>496</v>
       </c>
@@ -16815,11 +16807,11 @@
         <v>2375</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="16" t="s">
         <v>903</v>
       </c>
       <c r="C40" s="25" t="s">
@@ -16861,7 +16853,7 @@
       <c r="O40" s="11">
         <v>0.1638</v>
       </c>
-      <c r="P40" s="48" t="s">
+      <c r="P40" s="18" t="s">
         <v>904</v>
       </c>
       <c r="Q40" s="12" t="s">
@@ -16942,7 +16934,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>83</v>
       </c>
@@ -17444,7 +17436,7 @@
       <c r="A50" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="B50" s="44" t="s">
+      <c r="B50" s="16" t="s">
         <v>1638</v>
       </c>
       <c r="C50" s="25" t="s">
@@ -17504,11 +17496,11 @@
       <c r="X50" s="38"/>
       <c r="Y50" s="1"/>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B51" s="44" t="s">
+      <c r="B51" s="16" t="s">
         <v>1570</v>
       </c>
       <c r="C51" s="25" t="s">
@@ -17550,10 +17542,10 @@
       <c r="O51" s="11">
         <v>0.90969999999999995</v>
       </c>
-      <c r="P51" s="48" t="s">
+      <c r="P51" s="18" t="s">
         <v>1571</v>
       </c>
-      <c r="Q51" s="48" t="s">
+      <c r="Q51" s="18" t="s">
         <v>1572</v>
       </c>
       <c r="R51" s="13" t="s">
@@ -17567,7 +17559,7 @@
       </c>
       <c r="Y51" s="1"/>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>272</v>
       </c>
@@ -17629,7 +17621,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>120</v>
       </c>
@@ -17691,7 +17683,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>218</v>
       </c>
@@ -18001,7 +17993,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A59" s="8" t="s">
         <v>67</v>
       </c>
@@ -18187,7 +18179,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>517</v>
       </c>
@@ -18311,7 +18303,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
         <v>598</v>
       </c>
@@ -18375,11 +18367,11 @@
       <c r="X64" s="38"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B65" s="44" t="s">
+      <c r="B65" s="16" t="s">
         <v>1287</v>
       </c>
       <c r="C65" s="25" t="s">
@@ -18485,10 +18477,10 @@
       <c r="O66" s="11">
         <v>0.9768</v>
       </c>
-      <c r="P66" s="47" t="s">
+      <c r="P66" s="44" t="s">
         <v>3367</v>
       </c>
-      <c r="Q66" s="47" t="s">
+      <c r="Q66" s="44" t="s">
         <v>3367</v>
       </c>
       <c r="R66" s="13" t="s">
@@ -18563,7 +18555,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>350</v>
       </c>
@@ -18811,11 +18803,11 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="16" t="s">
         <v>1499</v>
       </c>
       <c r="C72" s="25" t="s">
@@ -18937,11 +18929,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="B74" s="44" t="s">
+      <c r="B74" s="16" t="s">
         <v>2202</v>
       </c>
       <c r="C74" s="25" t="s">
@@ -19253,7 +19245,7 @@
       <c r="A79" s="8" t="s">
         <v>556</v>
       </c>
-      <c r="B79" s="44" t="s">
+      <c r="B79" s="16" t="s">
         <v>2584</v>
       </c>
       <c r="C79" s="25" t="s">
@@ -19561,7 +19553,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>19</v>
       </c>
@@ -19815,7 +19807,7 @@
       <c r="A88" s="8" t="s">
         <v>567</v>
       </c>
-      <c r="B88" s="44" t="s">
+      <c r="B88" s="16" t="s">
         <v>2616</v>
       </c>
       <c r="C88" s="25" t="s">
@@ -20191,7 +20183,7 @@
       <c r="A94" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="B94" s="44" t="s">
+      <c r="B94" s="16" t="s">
         <v>2796</v>
       </c>
       <c r="C94" s="25" t="s">
@@ -20236,7 +20228,7 @@
       <c r="P94" s="12" t="s">
         <v>2797</v>
       </c>
-      <c r="Q94" s="48" t="s">
+      <c r="Q94" s="18" t="s">
         <v>2798</v>
       </c>
       <c r="R94" s="13" t="s">
@@ -20251,7 +20243,7 @@
       <c r="X94" s="38"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>280</v>
       </c>
@@ -20375,11 +20367,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="B97" s="44" t="s">
+      <c r="B97" s="16" t="s">
         <v>2080</v>
       </c>
       <c r="C97" s="25" t="s">
@@ -20439,7 +20431,7 @@
       <c r="X97" s="38"/>
       <c r="Y97" s="1"/>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>12</v>
       </c>
@@ -20625,7 +20617,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>467</v>
       </c>
@@ -20687,7 +20679,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>153</v>
       </c>
@@ -20749,7 +20741,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" s="8" t="s">
         <v>687</v>
       </c>
@@ -20811,7 +20803,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
         <v>461</v>
       </c>
@@ -20935,7 +20927,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>255</v>
       </c>
@@ -21183,7 +21175,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>627</v>
       </c>
@@ -21245,7 +21237,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>443</v>
       </c>
@@ -21309,7 +21301,7 @@
       <c r="X111" s="38"/>
       <c r="Y111" s="1"/>
     </row>
-    <row r="112" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="8" t="s">
         <v>450</v>
       </c>
@@ -21371,7 +21363,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="113" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>582</v>
       </c>
@@ -21565,7 +21557,7 @@
       <c r="W115" s="7"/>
       <c r="X115" s="7"/>
     </row>
-    <row r="116" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116" s="8" t="s">
         <v>381</v>
       </c>
@@ -21895,7 +21887,7 @@
       <c r="W120" s="7"/>
       <c r="X120" s="7"/>
     </row>
-    <row r="121" spans="1:24" ht="72" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>415</v>
       </c>
@@ -21961,7 +21953,7 @@
       <c r="W121" s="7"/>
       <c r="X121" s="7"/>
     </row>
-    <row r="122" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>514</v>
       </c>
@@ -22027,7 +22019,7 @@
       <c r="W122" s="7"/>
       <c r="X122" s="7"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>273</v>
       </c>
@@ -22093,7 +22085,7 @@
       <c r="W123" s="7"/>
       <c r="X123" s="7"/>
     </row>
-    <row r="124" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>214</v>
       </c>
@@ -22291,7 +22283,7 @@
       <c r="W126" s="7"/>
       <c r="X126" s="7"/>
     </row>
-    <row r="127" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>86</v>
       </c>
@@ -22489,7 +22481,7 @@
       <c r="W129" s="7"/>
       <c r="X129" s="7"/>
     </row>
-    <row r="130" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>354</v>
       </c>
@@ -22675,7 +22667,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="133" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A133" s="8" t="s">
         <v>348</v>
       </c>
@@ -22737,7 +22729,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="134" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134" s="8" t="s">
         <v>216</v>
       </c>
@@ -22799,7 +22791,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="135" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>663</v>
       </c>
@@ -23171,7 +23163,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>185</v>
       </c>
@@ -23419,11 +23411,11 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B145" s="44" t="s">
+      <c r="B145" s="16" t="s">
         <v>1530</v>
       </c>
       <c r="C145" s="25" t="s">
@@ -23731,7 +23723,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150" s="8" t="s">
         <v>247</v>
       </c>
@@ -23777,10 +23769,10 @@
       <c r="O150" s="11">
         <v>0.95799999999999996</v>
       </c>
-      <c r="P150" s="47" t="s">
+      <c r="P150" s="44" t="s">
         <v>3416</v>
       </c>
-      <c r="Q150" s="50" t="s">
+      <c r="Q150" s="46" t="s">
         <v>3418</v>
       </c>
       <c r="R150" s="13" t="s">
@@ -23797,7 +23789,7 @@
       <c r="A151" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="B151" s="44" t="s">
+      <c r="B151" s="16" t="s">
         <v>2412</v>
       </c>
       <c r="C151" s="25" t="s">
@@ -23981,7 +23973,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>228</v>
       </c>
@@ -24043,7 +24035,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="8" t="s">
         <v>311</v>
       </c>
@@ -24167,7 +24159,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="8" t="s">
         <v>617</v>
       </c>
@@ -24229,7 +24221,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="8" t="s">
         <v>170</v>
       </c>
@@ -24415,7 +24407,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="161" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>302</v>
       </c>
@@ -24477,7 +24469,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="162" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>630</v>
       </c>
@@ -24586,10 +24578,10 @@
       <c r="O163" s="11">
         <v>0.65610000000000002</v>
       </c>
-      <c r="P163" s="47" t="s">
+      <c r="P163" s="44" t="s">
         <v>3221</v>
       </c>
-      <c r="Q163" s="50" t="s">
+      <c r="Q163" s="46" t="s">
         <v>3223</v>
       </c>
       <c r="R163" s="13" t="s">
@@ -24729,7 +24721,7 @@
       </c>
       <c r="X165" s="7"/>
     </row>
-    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>226</v>
       </c>
@@ -24918,7 +24910,7 @@
       </c>
       <c r="X168" s="7"/>
     </row>
-    <row r="169" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>505</v>
       </c>
@@ -25488,7 +25480,7 @@
       </c>
       <c r="X177" s="7"/>
     </row>
-    <row r="178" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>438</v>
       </c>
@@ -25550,7 +25542,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>631</v>
       </c>
@@ -25736,7 +25728,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182" s="8" t="s">
         <v>306</v>
       </c>
@@ -25798,7 +25790,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>420</v>
       </c>
@@ -25984,7 +25976,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
         <v>485</v>
       </c>
@@ -26046,7 +26038,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
         <v>692</v>
       </c>
@@ -26234,7 +26226,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A190" s="8" t="s">
         <v>181</v>
       </c>
@@ -26296,7 +26288,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A191" s="8" t="s">
         <v>110</v>
       </c>
@@ -26362,7 +26354,7 @@
       <c r="A192" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B192" s="44" t="s">
+      <c r="B192" s="16" t="s">
         <v>2156</v>
       </c>
       <c r="C192" s="25" t="s">
@@ -26422,7 +26414,7 @@
       <c r="X192" s="38"/>
       <c r="Y192" s="1"/>
     </row>
-    <row r="193" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193" s="8" t="s">
         <v>281</v>
       </c>
@@ -26610,7 +26602,7 @@
       <c r="X195" s="38"/>
       <c r="Y195" s="1"/>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>668</v>
       </c>
@@ -26672,7 +26664,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A197" s="8" t="s">
         <v>497</v>
       </c>
@@ -27110,7 +27102,7 @@
       <c r="A204" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="B204" s="44" t="s">
+      <c r="B204" s="16" t="s">
         <v>1640</v>
       </c>
       <c r="C204" s="25" t="s">
@@ -27152,10 +27144,10 @@
       <c r="O204" s="11">
         <v>0.62150000000000005</v>
       </c>
-      <c r="P204" s="48" t="s">
+      <c r="P204" s="18" t="s">
         <v>1641</v>
       </c>
-      <c r="Q204" s="48" t="s">
+      <c r="Q204" s="18" t="s">
         <v>1641</v>
       </c>
       <c r="R204" s="13" t="s">
@@ -27357,7 +27349,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A208" s="8" t="s">
         <v>322</v>
       </c>
@@ -27483,7 +27475,7 @@
       <c r="X209" s="38"/>
       <c r="Y209" s="1"/>
     </row>
-    <row r="210" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210" s="8" t="s">
         <v>353</v>
       </c>
@@ -28077,7 +28069,7 @@
       <c r="W218" s="7"/>
       <c r="X218" s="7"/>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A219" s="8" t="s">
         <v>148</v>
       </c>
@@ -28209,7 +28201,7 @@
       <c r="W220" s="7"/>
       <c r="X220" s="7"/>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A221" s="8" t="s">
         <v>462</v>
       </c>
@@ -28726,7 +28718,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="8" t="s">
         <v>145</v>
       </c>
@@ -28914,7 +28906,7 @@
       <c r="X231" s="38"/>
       <c r="Y231" s="1"/>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="8" t="s">
         <v>480</v>
       </c>
@@ -28976,7 +28968,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A233" s="8" t="s">
         <v>593</v>
       </c>
@@ -29022,10 +29014,10 @@
       <c r="O233" s="11">
         <v>0.8992</v>
       </c>
-      <c r="P233" s="47" t="s">
+      <c r="P233" s="44" t="s">
         <v>3778</v>
       </c>
-      <c r="Q233" s="47" t="s">
+      <c r="Q233" s="44" t="s">
         <v>3778</v>
       </c>
       <c r="R233" s="13" t="s">
@@ -29102,7 +29094,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="8" t="s">
         <v>25</v>
       </c>
@@ -29413,7 +29405,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="8" t="s">
         <v>95</v>
       </c>
@@ -29537,7 +29529,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="8" t="s">
         <v>518</v>
       </c>
@@ -29599,11 +29591,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A243" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="B243" s="44" t="s">
+      <c r="B243" s="16" t="s">
         <v>2504</v>
       </c>
       <c r="C243" s="25" t="s">
@@ -29645,10 +29637,10 @@
       <c r="O243" s="11">
         <v>0.70679999999999998</v>
       </c>
-      <c r="P243" s="48" t="s">
+      <c r="P243" s="18" t="s">
         <v>2505</v>
       </c>
-      <c r="Q243" s="48" t="s">
+      <c r="Q243" s="18" t="s">
         <v>2506</v>
       </c>
       <c r="R243" s="13" t="s">
@@ -30020,10 +30012,10 @@
       <c r="O249" s="11">
         <v>0.2346</v>
       </c>
-      <c r="P249" s="48" t="s">
+      <c r="P249" s="18" t="s">
         <v>3000</v>
       </c>
-      <c r="Q249" s="48" t="s">
+      <c r="Q249" s="18" t="s">
         <v>3000</v>
       </c>
       <c r="R249" s="13" t="s">
@@ -30104,7 +30096,7 @@
       <c r="A251" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B251" s="44" t="s">
+      <c r="B251" s="16" t="s">
         <v>959</v>
       </c>
       <c r="C251" s="25" t="s">
@@ -30226,7 +30218,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="8" t="s">
         <v>124</v>
       </c>
@@ -30536,7 +30528,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A258" s="8" t="s">
         <v>244</v>
       </c>
@@ -30598,7 +30590,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259" s="8" t="s">
         <v>90</v>
       </c>
@@ -30660,11 +30652,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="B260" s="44" t="s">
+      <c r="B260" s="16" t="s">
         <v>2196</v>
       </c>
       <c r="C260" s="25" t="s">
@@ -30706,10 +30698,10 @@
       <c r="O260" s="11">
         <v>0.98599999999999999</v>
       </c>
-      <c r="P260" s="48" t="s">
+      <c r="P260" s="18" t="s">
         <v>2197</v>
       </c>
-      <c r="Q260" s="48" t="s">
+      <c r="Q260" s="18" t="s">
         <v>2197</v>
       </c>
       <c r="R260" s="13" t="s">
@@ -30725,7 +30717,7 @@
       <c r="X260" s="38"/>
       <c r="Y260" s="1"/>
     </row>
-    <row r="261" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261" s="8" t="s">
         <v>386</v>
       </c>
@@ -30914,11 +30906,11 @@
         <v>740</v>
       </c>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A264" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="B264" s="44" t="s">
+      <c r="B264" s="16" t="s">
         <v>1961</v>
       </c>
       <c r="C264" s="25" t="s">
@@ -30963,7 +30955,7 @@
       <c r="P264" s="12" t="s">
         <v>1962</v>
       </c>
-      <c r="Q264" s="48" t="s">
+      <c r="Q264" s="18" t="s">
         <v>1962</v>
       </c>
       <c r="R264" s="13" t="s">
@@ -31043,7 +31035,7 @@
       <c r="A266" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B266" s="44" t="s">
+      <c r="B266" s="16" t="s">
         <v>2029</v>
       </c>
       <c r="C266" s="25" t="s">
@@ -31273,10 +31265,10 @@
       <c r="O269" s="11">
         <v>0.98599999999999999</v>
       </c>
-      <c r="P269" s="47" t="s">
+      <c r="P269" s="44" t="s">
         <v>3473</v>
       </c>
-      <c r="Q269" s="47" t="s">
+      <c r="Q269" s="44" t="s">
         <v>3473</v>
       </c>
       <c r="R269" s="13" t="s">
@@ -31413,7 +31405,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272" s="8" t="s">
         <v>651</v>
       </c>
@@ -31541,7 +31533,7 @@
       <c r="A274" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="B274" s="44" t="s">
+      <c r="B274" s="16" t="s">
         <v>1948</v>
       </c>
       <c r="C274" s="25" t="s">
@@ -31602,11 +31594,11 @@
       <c r="X274" s="39"/>
       <c r="Y274" s="1"/>
     </row>
-    <row r="275" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B275" s="44" t="s">
+      <c r="B275" s="16" t="s">
         <v>1143</v>
       </c>
       <c r="C275" s="25" t="s">
@@ -31854,7 +31846,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279" s="8" t="s">
         <v>53</v>
       </c>
@@ -32044,7 +32036,7 @@
       <c r="A282" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="B282" s="45" t="s">
+      <c r="B282" s="7" t="s">
         <v>3434</v>
       </c>
       <c r="C282" s="25" t="s">
@@ -32105,7 +32097,7 @@
       <c r="X282" s="39"/>
       <c r="Y282" s="1"/>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" ht="72" x14ac:dyDescent="0.3">
       <c r="A283" s="8" t="s">
         <v>469</v>
       </c>
@@ -32154,7 +32146,7 @@
       <c r="P283" s="12" t="s">
         <v>904</v>
       </c>
-      <c r="Q283" s="50" t="s">
+      <c r="Q283" s="46" t="s">
         <v>3643</v>
       </c>
       <c r="R283" s="13" t="s">
@@ -32601,11 +32593,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="B291" s="44" t="s">
+      <c r="B291" s="16" t="s">
         <v>2527</v>
       </c>
       <c r="C291" s="25" t="s">
@@ -32650,7 +32642,7 @@
       <c r="P291" s="12" t="s">
         <v>2528</v>
       </c>
-      <c r="Q291" s="48" t="s">
+      <c r="Q291" s="18" t="s">
         <v>2529</v>
       </c>
       <c r="R291" s="13" t="s">
@@ -32664,7 +32656,7 @@
       </c>
       <c r="Y291" s="1"/>
     </row>
-    <row r="292" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292" s="8" t="s">
         <v>77</v>
       </c>
@@ -32792,7 +32784,7 @@
       <c r="X293" s="38"/>
       <c r="Y293" s="1"/>
     </row>
-    <row r="294" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294" s="8" t="s">
         <v>390</v>
       </c>
@@ -32920,7 +32912,7 @@
       <c r="A296" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="B296" s="44" t="s">
+      <c r="B296" s="16" t="s">
         <v>1978</v>
       </c>
       <c r="C296" s="25" t="s">
@@ -32965,7 +32957,7 @@
       <c r="P296" s="12" t="s">
         <v>1979</v>
       </c>
-      <c r="Q296" s="48" t="s">
+      <c r="Q296" s="18" t="s">
         <v>1979</v>
       </c>
       <c r="R296" s="13" t="s">
@@ -32980,7 +32972,7 @@
       <c r="X296" s="38"/>
       <c r="Y296" s="1"/>
     </row>
-    <row r="297" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="8" t="s">
         <v>574</v>
       </c>
@@ -33106,11 +33098,11 @@
       <c r="X298" s="38"/>
       <c r="Y298" s="1"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A299" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B299" s="44" t="s">
+      <c r="B299" s="16" t="s">
         <v>2599</v>
       </c>
       <c r="C299" s="25" t="s">
@@ -33155,7 +33147,7 @@
       <c r="P299" s="12" t="s">
         <v>2600</v>
       </c>
-      <c r="Q299" s="48" t="s">
+      <c r="Q299" s="18" t="s">
         <v>2601</v>
       </c>
       <c r="R299" s="13" t="s">
@@ -33360,7 +33352,7 @@
       <c r="A303" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B303" s="44" t="s">
+      <c r="B303" s="16" t="s">
         <v>1813</v>
       </c>
       <c r="C303" s="25" t="s">
@@ -33402,10 +33394,10 @@
       <c r="O303" s="11">
         <v>0.83430000000000004</v>
       </c>
-      <c r="P303" s="48" t="s">
+      <c r="P303" s="18" t="s">
         <v>1814</v>
       </c>
-      <c r="Q303" s="48" t="s">
+      <c r="Q303" s="18" t="s">
         <v>1814</v>
       </c>
       <c r="R303" s="13" t="s">
@@ -33607,7 +33599,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="307" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="8" t="s">
         <v>584</v>
       </c>
@@ -33921,7 +33913,7 @@
       <c r="X311" s="38"/>
       <c r="Y311" s="1"/>
     </row>
-    <row r="312" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312" s="8" t="s">
         <v>433</v>
       </c>
@@ -34417,7 +34409,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A320" s="8" t="s">
         <v>481</v>
       </c>
@@ -34466,7 +34458,7 @@
       <c r="P320" s="12" t="s">
         <v>2322</v>
       </c>
-      <c r="Q320" s="51" t="s">
+      <c r="Q320" s="47" t="s">
         <v>3672</v>
       </c>
       <c r="R320" s="13" t="s">
@@ -34667,11 +34659,11 @@
       <c r="X323" s="38"/>
       <c r="Y323" s="1"/>
     </row>
-    <row r="324" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A324" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="B324" s="44" t="s">
+      <c r="B324" s="16" t="s">
         <v>1886</v>
       </c>
       <c r="C324" s="25" t="s">
@@ -34793,7 +34785,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="326" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A326" s="8" t="s">
         <v>711</v>
       </c>
@@ -35107,7 +35099,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A331" s="8" t="s">
         <v>660</v>
       </c>
@@ -35153,10 +35145,10 @@
       <c r="O331" s="11">
         <v>0.92479999999999996</v>
       </c>
-      <c r="P331" s="47" t="s">
+      <c r="P331" s="44" t="s">
         <v>3850</v>
       </c>
-      <c r="Q331" s="50" t="s">
+      <c r="Q331" s="46" t="s">
         <v>3852</v>
       </c>
       <c r="R331" s="13" t="s">
@@ -35231,11 +35223,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A333" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B333" s="44" t="s">
+      <c r="B333" s="16" t="s">
         <v>1473</v>
       </c>
       <c r="C333" s="25" t="s">
@@ -35419,7 +35411,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="336" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A336" s="8" t="s">
         <v>709</v>
       </c>
@@ -35791,11 +35783,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A342" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B342" s="44" t="s">
+      <c r="B342" s="16" t="s">
         <v>920</v>
       </c>
       <c r="C342" s="25" t="s">
@@ -35917,7 +35909,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A344" s="8" t="s">
         <v>146</v>
       </c>
@@ -35979,7 +35971,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A345" s="8" t="s">
         <v>315</v>
       </c>
@@ -36103,7 +36095,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A347" s="8" t="s">
         <v>154</v>
       </c>
@@ -36227,11 +36219,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="349" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A349" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="B349" s="44" t="s">
+      <c r="B349" s="16" t="s">
         <v>2559</v>
       </c>
       <c r="C349" s="25" t="s">
@@ -36292,14 +36284,14 @@
       <c r="X349" s="38"/>
       <c r="Y349" s="1"/>
     </row>
-    <row r="350" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A350" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B350" s="44" t="s">
+      <c r="B350" s="16" t="s">
         <v>1923</v>
       </c>
-      <c r="C350" s="46" t="s">
+      <c r="C350" s="1" t="s">
         <v>3522</v>
       </c>
       <c r="D350" s="10">
@@ -36357,7 +36349,7 @@
       <c r="V350" s="39"/>
       <c r="Y350" s="1"/>
     </row>
-    <row r="351" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A351" s="8" t="s">
         <v>649</v>
       </c>
@@ -36419,7 +36411,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="352" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A352" s="8" t="s">
         <v>101</v>
       </c>
@@ -36543,7 +36535,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="354" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A354" s="8" t="s">
         <v>395</v>
       </c>
@@ -36667,7 +36659,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A356" s="8" t="s">
         <v>136</v>
       </c>
@@ -36729,7 +36721,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="357" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A357" s="8" t="s">
         <v>398</v>
       </c>
@@ -37043,7 +37035,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A362" s="8" t="s">
         <v>100</v>
       </c>
@@ -37229,7 +37221,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A365" s="8" t="s">
         <v>533</v>
       </c>
@@ -37477,11 +37469,11 @@
         <v>733</v>
       </c>
     </row>
-    <row r="369" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369" s="8" t="s">
         <v>654</v>
       </c>
-      <c r="B369" s="44" t="s">
+      <c r="B369" s="16" t="s">
         <v>2902</v>
       </c>
       <c r="C369" s="25" t="s">
@@ -37605,7 +37597,7 @@
       <c r="X370" s="38"/>
       <c r="Y370" s="1"/>
     </row>
-    <row r="371" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371" s="8" t="s">
         <v>297</v>
       </c>
@@ -37654,7 +37646,7 @@
       <c r="P371" s="12" t="s">
         <v>1827</v>
       </c>
-      <c r="Q371" s="50" t="s">
+      <c r="Q371" s="46" t="s">
         <v>3485</v>
       </c>
       <c r="R371" s="13" t="s">
@@ -38229,7 +38221,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="381" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A381" s="8" t="s">
         <v>446</v>
       </c>
@@ -38291,7 +38283,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A382" s="8" t="s">
         <v>644</v>
       </c>
@@ -38357,7 +38349,7 @@
       <c r="A383" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B383" s="44" t="s">
+      <c r="B383" s="16" t="s">
         <v>837</v>
       </c>
       <c r="C383" s="25" t="s">
@@ -38665,7 +38657,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A388" s="8" t="s">
         <v>289</v>
       </c>
@@ -38714,7 +38706,7 @@
       <c r="P388" s="12" t="s">
         <v>1809</v>
       </c>
-      <c r="Q388" s="50" t="s">
+      <c r="Q388" s="46" t="s">
         <v>3469</v>
       </c>
       <c r="R388" s="13" t="s">
@@ -38789,7 +38781,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A390" s="8" t="s">
         <v>108</v>
       </c>
@@ -38913,7 +38905,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A392" s="8" t="s">
         <v>628</v>
       </c>
@@ -39021,10 +39013,10 @@
       <c r="O393" s="11">
         <v>0.95799999999999996</v>
       </c>
-      <c r="P393" s="47" t="s">
+      <c r="P393" s="44" t="s">
         <v>3883</v>
       </c>
-      <c r="Q393" s="50" t="s">
+      <c r="Q393" s="46" t="s">
         <v>3885</v>
       </c>
       <c r="R393" s="13" t="s">
@@ -39041,7 +39033,7 @@
       <c r="A394" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B394" s="44" t="s">
+      <c r="B394" s="16" t="s">
         <v>992</v>
       </c>
       <c r="C394" s="25" t="s">
@@ -39231,7 +39223,7 @@
       <c r="A397" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B397" s="44" t="s">
+      <c r="B397" s="16" t="s">
         <v>1650</v>
       </c>
       <c r="C397" s="25" t="s">
@@ -39415,7 +39407,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A400" s="8" t="s">
         <v>109</v>
       </c>
@@ -39803,7 +39795,7 @@
       <c r="W405" s="7"/>
       <c r="X405" s="7"/>
     </row>
-    <row r="406" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:24" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A406" s="8" t="s">
         <v>70</v>
       </c>
@@ -39869,7 +39861,7 @@
       <c r="W406" s="7"/>
       <c r="X406" s="7"/>
     </row>
-    <row r="407" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A407" s="8" t="s">
         <v>294</v>
       </c>
@@ -39918,7 +39910,7 @@
       <c r="P407" s="12" t="s">
         <v>1820</v>
       </c>
-      <c r="Q407" s="50" t="s">
+      <c r="Q407" s="46" t="s">
         <v>3479</v>
       </c>
       <c r="R407" s="13" t="s">
@@ -40001,7 +39993,7 @@
       <c r="W408" s="7"/>
       <c r="X408" s="7"/>
     </row>
-    <row r="409" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A409" s="8" t="s">
         <v>676</v>
       </c>
@@ -40463,7 +40455,7 @@
       <c r="W415" s="7"/>
       <c r="X415" s="7"/>
     </row>
-    <row r="416" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A416" s="8" t="s">
         <v>618</v>
       </c>
@@ -40512,7 +40504,7 @@
       <c r="P416" s="12" t="s">
         <v>2793</v>
       </c>
-      <c r="Q416" s="50" t="s">
+      <c r="Q416" s="46" t="s">
         <v>3803</v>
       </c>
       <c r="R416" s="13" t="s">
@@ -40720,7 +40712,7 @@
       </c>
       <c r="Y419" s="1"/>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A420" s="8" t="s">
         <v>128</v>
       </c>
@@ -41092,7 +41084,7 @@
         <v>2182</v>
       </c>
     </row>
-    <row r="426" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A426" s="8" t="s">
         <v>595</v>
       </c>
@@ -41218,7 +41210,7 @@
       <c r="X427" s="38"/>
       <c r="Y427" s="1"/>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A428" s="8" t="s">
         <v>98</v>
       </c>
@@ -41528,7 +41520,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A433" s="8" t="s">
         <v>444</v>
       </c>
@@ -41590,7 +41582,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A434" s="8" t="s">
         <v>13</v>
       </c>
@@ -41714,7 +41706,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A436" s="8" t="s">
         <v>397</v>
       </c>
@@ -41840,7 +41832,7 @@
       <c r="X437" s="38"/>
       <c r="Y437" s="1"/>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A438" s="8" t="s">
         <v>143</v>
       </c>
@@ -41966,7 +41958,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A440" s="8" t="s">
         <v>66</v>
       </c>
@@ -42028,7 +42020,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A441" s="8" t="s">
         <v>502</v>
       </c>
@@ -42077,7 +42069,7 @@
       <c r="P441" s="12" t="s">
         <v>2396</v>
       </c>
-      <c r="Q441" s="50" t="s">
+      <c r="Q441" s="46" t="s">
         <v>3692</v>
       </c>
       <c r="R441" s="13" t="s">
@@ -42152,7 +42144,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="443" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A443" s="8" t="s">
         <v>38</v>
       </c>
@@ -42198,7 +42190,7 @@
       <c r="O443" s="11">
         <v>0.98599999999999999</v>
       </c>
-      <c r="P443" s="47" t="s">
+      <c r="P443" s="44" t="s">
         <v>909</v>
       </c>
       <c r="Q443" s="12" t="s">
@@ -42218,7 +42210,7 @@
       <c r="A444" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="B444" s="44" t="s">
+      <c r="B444" s="16" t="s">
         <v>1986</v>
       </c>
       <c r="C444" s="25" t="s">
@@ -42282,7 +42274,7 @@
       <c r="A445" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="B445" s="44" t="s">
+      <c r="B445" s="16" t="s">
         <v>1992</v>
       </c>
       <c r="C445" s="25" t="s">
@@ -42342,7 +42334,7 @@
       <c r="X445" s="38"/>
       <c r="Y445" s="1"/>
     </row>
-    <row r="446" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446" s="8" t="s">
         <v>27</v>
       </c>
@@ -42466,7 +42458,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="448" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A448" s="8" t="s">
         <v>301</v>
       </c>
@@ -42512,10 +42504,10 @@
       <c r="O448" s="11">
         <v>0.77070000000000005</v>
       </c>
-      <c r="P448" s="47" t="s">
+      <c r="P448" s="44" t="s">
         <v>3489</v>
       </c>
-      <c r="Q448" s="47" t="s">
+      <c r="Q448" s="44" t="s">
         <v>3489</v>
       </c>
       <c r="R448" s="13" t="s">
@@ -43184,7 +43176,7 @@
       <c r="W458" s="7"/>
       <c r="X458" s="7"/>
     </row>
-    <row r="459" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A459" s="8" t="s">
         <v>160</v>
       </c>
@@ -43382,7 +43374,7 @@
       <c r="W461" s="7"/>
       <c r="X461" s="7"/>
     </row>
-    <row r="462" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:24" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A462" s="8" t="s">
         <v>620</v>
       </c>
@@ -43448,7 +43440,7 @@
       <c r="W462" s="7"/>
       <c r="X462" s="7"/>
     </row>
-    <row r="463" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:24" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A463" s="8" t="s">
         <v>195</v>
       </c>
@@ -43629,7 +43621,7 @@
       <c r="P465" s="12" t="s">
         <v>1744</v>
       </c>
-      <c r="Q465" s="50" t="s">
+      <c r="Q465" s="46" t="s">
         <v>3439</v>
       </c>
       <c r="R465" s="13" t="s">
@@ -43770,7 +43762,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A468" s="8" t="s">
         <v>34</v>
       </c>
@@ -43819,7 +43811,7 @@
       <c r="P468" s="12" t="s">
         <v>893</v>
       </c>
-      <c r="Q468" s="47" t="s">
+      <c r="Q468" s="44" t="s">
         <v>893</v>
       </c>
       <c r="R468" s="13" t="s">
@@ -43832,7 +43824,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A469" s="8" t="s">
         <v>310</v>
       </c>
@@ -43958,11 +43950,11 @@
       <c r="X470" s="38"/>
       <c r="Y470" s="1"/>
     </row>
-    <row r="471" spans="1:25" ht="72" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A471" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B471" s="44" t="s">
+      <c r="B471" s="16" t="s">
         <v>1541</v>
       </c>
       <c r="C471" s="25" t="s">
@@ -44007,7 +43999,7 @@
       <c r="P471" s="12" t="s">
         <v>1542</v>
       </c>
-      <c r="Q471" s="48" t="s">
+      <c r="Q471" s="18" t="s">
         <v>1542</v>
       </c>
       <c r="R471" s="13" t="s">
@@ -44022,11 +44014,11 @@
       <c r="X471" s="38"/>
       <c r="Y471" s="1"/>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A472" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B472" s="44" t="s">
+      <c r="B472" s="16" t="s">
         <v>887</v>
       </c>
       <c r="C472" s="25" t="s">
@@ -44151,11 +44143,11 @@
       <c r="X473" s="38"/>
       <c r="Y473" s="1"/>
     </row>
-    <row r="474" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A474" s="8" t="s">
         <v>586</v>
       </c>
-      <c r="B474" s="44" t="s">
+      <c r="B474" s="16" t="s">
         <v>2670</v>
       </c>
       <c r="C474" s="25" t="s">
@@ -44200,7 +44192,7 @@
       <c r="P474" s="12" t="s">
         <v>2671</v>
       </c>
-      <c r="Q474" s="48" t="s">
+      <c r="Q474" s="18" t="s">
         <v>2672</v>
       </c>
       <c r="R474" s="13" t="s">
@@ -44215,7 +44207,7 @@
       <c r="X474" s="38"/>
       <c r="Y474" s="1"/>
     </row>
-    <row r="475" spans="1:25" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A475" s="8" t="s">
         <v>706</v>
       </c>
@@ -44261,7 +44253,7 @@
       <c r="O475" s="11">
         <v>0.50319999999999998</v>
       </c>
-      <c r="P475" s="47" t="s">
+      <c r="P475" s="44" t="s">
         <v>3908</v>
       </c>
       <c r="Q475" s="26" t="s">
@@ -44344,11 +44336,11 @@
       <c r="X476" s="38"/>
       <c r="Y476" s="1"/>
     </row>
-    <row r="477" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A477" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="B477" s="44" t="s">
+      <c r="B477" s="16" t="s">
         <v>2288</v>
       </c>
       <c r="C477" s="25" t="s">
@@ -44540,7 +44532,7 @@
       <c r="A480" s="8" t="s">
         <v>558</v>
       </c>
-      <c r="B480" s="44" t="s">
+      <c r="B480" s="16" t="s">
         <v>2590</v>
       </c>
       <c r="C480" s="25" t="s">
@@ -44582,10 +44574,10 @@
       <c r="O480" s="11">
         <v>0.9425</v>
       </c>
-      <c r="P480" s="48" t="s">
+      <c r="P480" s="18" t="s">
         <v>2591</v>
       </c>
-      <c r="Q480" s="48" t="s">
+      <c r="Q480" s="18" t="s">
         <v>2592</v>
       </c>
       <c r="R480" s="13" t="s">
@@ -44664,11 +44656,11 @@
       <c r="X481" s="38"/>
       <c r="Y481" s="1"/>
     </row>
-    <row r="482" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A482" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="B482" s="44" t="s">
+      <c r="B482" s="16" t="s">
         <v>1757</v>
       </c>
       <c r="C482" s="25" t="s">
@@ -44728,11 +44720,11 @@
       <c r="X482" s="38"/>
       <c r="Y482" s="1"/>
     </row>
-    <row r="483" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A483" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B483" s="44" t="s">
+      <c r="B483" s="16" t="s">
         <v>1228</v>
       </c>
       <c r="C483" s="25" t="s">
@@ -44777,7 +44769,7 @@
       <c r="P483" s="12" t="s">
         <v>1229</v>
       </c>
-      <c r="Q483" s="48" t="s">
+      <c r="Q483" s="18" t="s">
         <v>1230</v>
       </c>
       <c r="R483" s="13" t="s">
@@ -44854,7 +44846,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="485" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A485" s="8" t="s">
         <v>686</v>
       </c>
@@ -44916,7 +44908,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="486" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A486" s="8" t="s">
         <v>24</v>
       </c>
@@ -44978,7 +44970,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="487" spans="1:25" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A487" s="8" t="s">
         <v>10</v>
       </c>
@@ -45040,7 +45032,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A488" s="8" t="s">
         <v>536</v>
       </c>
@@ -45106,7 +45098,7 @@
       <c r="A489" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="B489" s="44" t="s">
+      <c r="B489" s="16" t="s">
         <v>2653</v>
       </c>
       <c r="C489" s="25" t="s">
@@ -45228,11 +45220,11 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A491" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="B491" s="44" t="s">
+      <c r="B491" s="16" t="s">
         <v>2682</v>
       </c>
       <c r="C491" s="25" t="s">
@@ -45480,7 +45472,7 @@
       <c r="X494" s="38"/>
       <c r="Y494" s="1"/>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A495" s="8" t="s">
         <v>152</v>
       </c>
@@ -45546,7 +45538,7 @@
       <c r="A496" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="B496" s="44" t="s">
+      <c r="B496" s="16" t="s">
         <v>2809</v>
       </c>
       <c r="C496" s="25" t="s">
@@ -45606,7 +45598,7 @@
       <c r="X496" s="38"/>
       <c r="Y496" s="1"/>
     </row>
-    <row r="497" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A497" s="8" t="s">
         <v>93</v>
       </c>
@@ -45668,7 +45660,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A498" s="8" t="s">
         <v>290</v>
       </c>
@@ -45730,7 +45722,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="499" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A499" s="8" t="s">
         <v>459</v>
       </c>
@@ -45792,7 +45784,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="500" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A500" s="8" t="s">
         <v>499</v>
       </c>
@@ -45900,10 +45892,10 @@
       <c r="O501" s="11">
         <v>0.99450000000000005</v>
       </c>
-      <c r="P501" s="47" t="s">
+      <c r="P501" s="44" t="s">
         <v>3918</v>
       </c>
-      <c r="Q501" s="50" t="s">
+      <c r="Q501" s="46" t="s">
         <v>3787</v>
       </c>
       <c r="R501" s="13" t="s">
@@ -46040,11 +46032,11 @@
         <v>2395</v>
       </c>
     </row>
-    <row r="504" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A504" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="B504" s="44" t="s">
+      <c r="B504" s="16" t="s">
         <v>1308</v>
       </c>
       <c r="C504" s="25" t="s">
@@ -46089,7 +46081,7 @@
       <c r="P504" s="12" t="s">
         <v>1309</v>
       </c>
-      <c r="Q504" s="48" t="s">
+      <c r="Q504" s="18" t="s">
         <v>1310</v>
       </c>
       <c r="R504" s="13" t="s">
@@ -46104,7 +46096,7 @@
       <c r="X504" s="38"/>
       <c r="Y504" s="1"/>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A505" s="8" t="s">
         <v>636</v>
       </c>
@@ -46232,7 +46224,7 @@
       <c r="A507" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B507" s="44" t="s">
+      <c r="B507" s="16" t="s">
         <v>1075</v>
       </c>
       <c r="C507" s="25" t="s">
@@ -46354,7 +46346,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A509" s="8" t="s">
         <v>257</v>
       </c>
@@ -46540,7 +46532,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="512" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A512" s="8" t="s">
         <v>411</v>
       </c>
@@ -46602,7 +46594,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A513" s="8" t="s">
         <v>680</v>
       </c>
@@ -46726,7 +46718,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="515" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A515" s="8" t="s">
         <v>413</v>
       </c>
@@ -46788,7 +46780,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="516" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A516" s="8" t="s">
         <v>682</v>
       </c>
@@ -46850,7 +46842,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="517" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A517" s="8" t="s">
         <v>531</v>
       </c>
@@ -46974,7 +46966,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="519" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A519" s="8" t="s">
         <v>511</v>
       </c>
@@ -47160,7 +47152,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="522" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A522" s="8" t="s">
         <v>639</v>
       </c>
@@ -47209,7 +47201,7 @@
       <c r="P522" s="12" t="s">
         <v>2853</v>
       </c>
-      <c r="Q522" s="48" t="s">
+      <c r="Q522" s="18" t="s">
         <v>2853</v>
       </c>
       <c r="R522" s="13" t="s">
@@ -47414,7 +47406,7 @@
       <c r="A526" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B526" s="44" t="s">
+      <c r="B526" s="16" t="s">
         <v>1646</v>
       </c>
       <c r="C526" s="25" t="s">
@@ -47456,10 +47448,10 @@
       <c r="O526" s="11">
         <v>0.92330000000000001</v>
       </c>
-      <c r="P526" s="48" t="s">
+      <c r="P526" s="18" t="s">
         <v>1647</v>
       </c>
-      <c r="Q526" s="48" t="s">
+      <c r="Q526" s="18" t="s">
         <v>1436</v>
       </c>
       <c r="R526" s="13" t="s">
@@ -47598,7 +47590,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="529" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A529" s="8" t="s">
         <v>436</v>
       </c>
@@ -47848,7 +47840,7 @@
         <v>2493</v>
       </c>
     </row>
-    <row r="533" spans="1:25" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A533" s="8" t="s">
         <v>155</v>
       </c>
@@ -47976,7 +47968,7 @@
       <c r="X534" s="38"/>
       <c r="Y534" s="1"/>
     </row>
-    <row r="535" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A535" s="8" t="s">
         <v>332</v>
       </c>
@@ -48038,7 +48030,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A536" s="8" t="s">
         <v>473</v>
       </c>
@@ -48087,7 +48079,7 @@
       <c r="P536" s="12" t="s">
         <v>2298</v>
       </c>
-      <c r="Q536" s="50" t="s">
+      <c r="Q536" s="46" t="s">
         <v>3653</v>
       </c>
       <c r="R536" s="13" t="s">
@@ -48722,7 +48714,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A547" s="8" t="s">
         <v>258</v>
       </c>
@@ -48768,10 +48760,10 @@
       <c r="O547" s="11">
         <v>0.98380000000000001</v>
       </c>
-      <c r="P547" s="47" t="s">
+      <c r="P547" s="44" t="s">
         <v>3431</v>
       </c>
-      <c r="Q547" s="47" t="s">
+      <c r="Q547" s="44" t="s">
         <v>3431</v>
       </c>
       <c r="R547" s="13" t="s">
@@ -48848,7 +48840,7 @@
       <c r="X548" s="38"/>
       <c r="Y548" s="1"/>
     </row>
-    <row r="549" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A549" s="8" t="s">
         <v>367</v>
       </c>
@@ -48972,7 +48964,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="551" spans="1:25" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A551" s="8" t="s">
         <v>232</v>
       </c>
@@ -49207,7 +49199,7 @@
       <c r="P554" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="Q554" s="50" t="s">
+      <c r="Q554" s="46" t="s">
         <v>3271</v>
       </c>
       <c r="R554" s="13" t="s">
@@ -49406,7 +49398,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A558" s="8" t="s">
         <v>99</v>
       </c>
@@ -49592,7 +49584,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="561" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A561" s="8" t="s">
         <v>151</v>
       </c>
@@ -49716,7 +49708,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="563" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A563" s="8" t="s">
         <v>380</v>
       </c>
@@ -49902,7 +49894,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="566" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A566" s="8" t="s">
         <v>604</v>
       </c>
@@ -50214,7 +50206,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="571" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A571" s="8" t="s">
         <v>498</v>
       </c>
@@ -50384,10 +50376,10 @@
       <c r="O573" s="11">
         <v>0.89900000000000002</v>
       </c>
-      <c r="P573" s="47" t="s">
+      <c r="P573" s="44" t="s">
         <v>3665</v>
       </c>
-      <c r="Q573" s="50" t="s">
+      <c r="Q573" s="46" t="s">
         <v>3667</v>
       </c>
       <c r="R573" s="13" t="s">
@@ -50402,7 +50394,7 @@
       <c r="U573" s="42"/>
       <c r="Z573" s="1"/>
     </row>
-    <row r="574" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A574" s="8" t="s">
         <v>238</v>
       </c>
@@ -50470,7 +50462,7 @@
       <c r="A575" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B575" s="44" t="s">
+      <c r="B575" s="16" t="s">
         <v>1323</v>
       </c>
       <c r="C575" s="25" t="s">
@@ -50532,7 +50524,7 @@
       <c r="Y575" s="1"/>
       <c r="Z575" s="1"/>
     </row>
-    <row r="576" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A576" s="8" t="s">
         <v>26</v>
       </c>
@@ -50726,7 +50718,7 @@
       <c r="U578" s="42"/>
       <c r="Z578" s="1"/>
     </row>
-    <row r="579" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A579" s="8" t="s">
         <v>233</v>
       </c>
@@ -50918,7 +50910,7 @@
       <c r="U581" s="42"/>
       <c r="Z581" s="1"/>
     </row>
-    <row r="582" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A582" s="8" t="s">
         <v>507</v>
       </c>
@@ -51048,7 +51040,7 @@
       <c r="Y583" s="1"/>
       <c r="Z583" s="1"/>
     </row>
-    <row r="584" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A584" s="8" t="s">
         <v>515</v>
       </c>
@@ -51112,7 +51104,7 @@
       <c r="U584" s="42"/>
       <c r="Z584" s="1"/>
     </row>
-    <row r="585" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A585" s="8" t="s">
         <v>328</v>
       </c>
@@ -51175,7 +51167,7 @@
       </c>
       <c r="Z585" s="1"/>
     </row>
-    <row r="586" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A586" s="8" t="s">
         <v>487</v>
       </c>
@@ -51364,7 +51356,7 @@
       </c>
       <c r="Z588" s="1"/>
     </row>
-    <row r="589" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A589" s="8" t="s">
         <v>241</v>
       </c>
@@ -51410,10 +51402,10 @@
       <c r="O589" s="11">
         <v>0.77070000000000005</v>
       </c>
-      <c r="P589" s="47" t="s">
+      <c r="P589" s="44" t="s">
         <v>3406</v>
       </c>
-      <c r="Q589" s="50" t="s">
+      <c r="Q589" s="46" t="s">
         <v>3408</v>
       </c>
       <c r="R589" s="13" t="s">
@@ -51427,7 +51419,7 @@
       </c>
       <c r="Z589" s="1"/>
     </row>
-    <row r="590" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A590" s="8" t="s">
         <v>43</v>
       </c>
@@ -51555,7 +51547,7 @@
       <c r="Y591" s="1"/>
       <c r="Z591" s="1"/>
     </row>
-    <row r="592" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A592" s="8" t="s">
         <v>683</v>
       </c>
@@ -51744,11 +51736,11 @@
       </c>
       <c r="Z594" s="1"/>
     </row>
-    <row r="595" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A595" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="B595" s="44" t="s">
+      <c r="B595" s="16" t="s">
         <v>1845</v>
       </c>
       <c r="C595" s="25" t="s">
@@ -51790,10 +51782,10 @@
       <c r="O595" s="11">
         <v>0.98819999999999997</v>
       </c>
-      <c r="P595" s="48" t="s">
+      <c r="P595" s="18" t="s">
         <v>1846</v>
       </c>
-      <c r="Q595" s="48" t="s">
+      <c r="Q595" s="18" t="s">
         <v>1847</v>
       </c>
       <c r="R595" s="13" t="s">
@@ -51872,7 +51864,7 @@
       </c>
       <c r="Z596" s="1"/>
     </row>
-    <row r="597" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A597" s="8" t="s">
         <v>352</v>
       </c>
@@ -52065,7 +52057,7 @@
       <c r="A600" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="B600" s="44" t="s">
+      <c r="B600" s="16" t="s">
         <v>2921</v>
       </c>
       <c r="C600" s="25" t="s">
@@ -52256,7 +52248,7 @@
       <c r="A603" s="8" t="s">
         <v>694</v>
       </c>
-      <c r="B603" s="44" t="s">
+      <c r="B603" s="16" t="s">
         <v>3024</v>
       </c>
       <c r="C603" s="25" t="s">
@@ -52298,10 +52290,10 @@
       <c r="O603" s="11">
         <v>0.96020000000000005</v>
       </c>
-      <c r="P603" s="48" t="s">
+      <c r="P603" s="18" t="s">
         <v>3025</v>
       </c>
-      <c r="Q603" s="48" t="s">
+      <c r="Q603" s="18" t="s">
         <v>3026</v>
       </c>
       <c r="R603" s="13" t="s">
@@ -52317,7 +52309,7 @@
       <c r="Y603" s="1"/>
       <c r="Z603" s="1"/>
     </row>
-    <row r="604" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A604" s="8" t="s">
         <v>274</v>
       </c>
@@ -52443,7 +52435,7 @@
       </c>
       <c r="Z605" s="1"/>
     </row>
-    <row r="606" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A606" s="8" t="s">
         <v>159</v>
       </c>
@@ -52506,7 +52498,7 @@
       </c>
       <c r="Z606" s="1"/>
     </row>
-    <row r="607" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A607" s="8" t="s">
         <v>63</v>
       </c>
@@ -52822,7 +52814,7 @@
       </c>
       <c r="Z611" s="1"/>
     </row>
-    <row r="612" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A612" s="8" t="s">
         <v>15</v>
       </c>
@@ -52889,7 +52881,7 @@
       <c r="A613" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="B613" s="44" t="s">
+      <c r="B613" s="16" t="s">
         <v>2190</v>
       </c>
       <c r="C613" s="25" t="s">
@@ -53013,11 +53005,11 @@
       </c>
       <c r="Z614" s="1"/>
     </row>
-    <row r="615" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A615" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="B615" s="44" t="s">
+      <c r="B615" s="16" t="s">
         <v>2115</v>
       </c>
       <c r="C615" s="25" t="s">
@@ -53078,7 +53070,7 @@
       <c r="Y615" s="1"/>
       <c r="Z615" s="1"/>
     </row>
-    <row r="616" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A616" s="8" t="s">
         <v>577</v>
       </c>
@@ -53313,10 +53305,10 @@
       <c r="O619" s="11">
         <v>0.95350000000000001</v>
       </c>
-      <c r="P619" s="47" t="s">
+      <c r="P619" s="44" t="s">
         <v>3897</v>
       </c>
-      <c r="Q619" s="50" t="s">
+      <c r="Q619" s="46" t="s">
         <v>3899</v>
       </c>
       <c r="R619" s="13" t="s">
@@ -53330,11 +53322,11 @@
       </c>
       <c r="Z619" s="1"/>
     </row>
-    <row r="620" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A620" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B620" s="44" t="s">
+      <c r="B620" s="16" t="s">
         <v>786</v>
       </c>
       <c r="C620" s="25" t="s">
@@ -53379,7 +53371,7 @@
       <c r="P620" s="12" t="s">
         <v>787</v>
       </c>
-      <c r="Q620" s="48" t="s">
+      <c r="Q620" s="18" t="s">
         <v>787</v>
       </c>
       <c r="R620" s="13" t="s">
@@ -53462,7 +53454,7 @@
       <c r="A622" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="B622" s="44" t="s">
+      <c r="B622" s="16" t="s">
         <v>1552</v>
       </c>
       <c r="C622" s="25" t="s">
@@ -53845,7 +53837,7 @@
       </c>
       <c r="Z627" s="1"/>
     </row>
-    <row r="628" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A628" s="8" t="s">
         <v>648</v>
       </c>
@@ -53908,11 +53900,11 @@
       </c>
       <c r="Z628" s="1"/>
     </row>
-    <row r="629" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A629" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B629" s="44" t="s">
+      <c r="B629" s="16" t="s">
         <v>1779</v>
       </c>
       <c r="C629" s="25" t="s">
@@ -53973,7 +53965,7 @@
       <c r="Y629" s="1"/>
       <c r="Z629" s="1"/>
     </row>
-    <row r="630" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A630" s="8" t="s">
         <v>472</v>
       </c>
@@ -54022,7 +54014,7 @@
       <c r="P630" s="12" t="s">
         <v>2295</v>
       </c>
-      <c r="Q630" s="50" t="s">
+      <c r="Q630" s="46" t="s">
         <v>3650</v>
       </c>
       <c r="R630" s="13" t="s">
@@ -54036,7 +54028,7 @@
       </c>
       <c r="Z630" s="1"/>
     </row>
-    <row r="631" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A631" s="8" t="s">
         <v>520</v>
       </c>
@@ -54085,7 +54077,7 @@
       <c r="P631" s="12" t="s">
         <v>2460</v>
       </c>
-      <c r="Q631" s="50" t="s">
+      <c r="Q631" s="46" t="s">
         <v>3088</v>
       </c>
       <c r="R631" s="13" t="s">
@@ -54099,11 +54091,11 @@
       </c>
       <c r="Z631" s="1"/>
     </row>
-    <row r="632" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A632" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="B632" s="44" t="s">
+      <c r="B632" s="16" t="s">
         <v>968</v>
       </c>
       <c r="C632" s="25" t="s">
@@ -54479,7 +54471,7 @@
       </c>
       <c r="Z637" s="1"/>
     </row>
-    <row r="638" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A638" s="8" t="s">
         <v>91</v>
       </c>
@@ -54605,7 +54597,7 @@
       </c>
       <c r="Z639" s="1"/>
     </row>
-    <row r="640" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A640" s="8" t="s">
         <v>173</v>
       </c>
@@ -54672,7 +54664,7 @@
       <c r="A641" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="B641" s="44" t="s">
+      <c r="B641" s="16" t="s">
         <v>2455</v>
       </c>
       <c r="C641" s="25" t="s">
@@ -55309,7 +55301,7 @@
       <c r="U650" s="42"/>
       <c r="Z650" s="1"/>
     </row>
-    <row r="651" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A651" s="8" t="s">
         <v>662</v>
       </c>
@@ -55373,11 +55365,11 @@
       <c r="U651" s="42"/>
       <c r="Z651" s="1"/>
     </row>
-    <row r="652" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A652" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="B652" s="44" t="s">
+      <c r="B652" s="16" t="s">
         <v>1461</v>
       </c>
       <c r="C652" s="25" t="s">
@@ -55953,7 +55945,7 @@
       <c r="U660" s="42"/>
       <c r="Z660" s="1"/>
     </row>
-    <row r="661" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A661" s="8" t="s">
         <v>82</v>
       </c>
@@ -56017,11 +56009,11 @@
       <c r="U661" s="42"/>
       <c r="Z661" s="1"/>
     </row>
-    <row r="662" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A662" s="8" t="s">
         <v>559</v>
       </c>
-      <c r="B662" s="44" t="s">
+      <c r="B662" s="16" t="s">
         <v>2593</v>
       </c>
       <c r="C662" s="25" t="s">
@@ -56063,10 +56055,10 @@
       <c r="O662" s="11">
         <v>0.84119999999999995</v>
       </c>
-      <c r="P662" s="49" t="s">
+      <c r="P662" s="45" t="s">
         <v>2594</v>
       </c>
-      <c r="Q662" s="48" t="s">
+      <c r="Q662" s="18" t="s">
         <v>2594</v>
       </c>
       <c r="R662" s="13" t="s">
@@ -56272,7 +56264,7 @@
       </c>
       <c r="Z665" s="1"/>
     </row>
-    <row r="666" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A666" s="8" t="s">
         <v>412</v>
       </c>
@@ -56591,7 +56583,7 @@
       </c>
       <c r="Z670" s="1"/>
     </row>
-    <row r="671" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A671" s="8" t="s">
         <v>264</v>
       </c>
@@ -56719,7 +56711,7 @@
       </c>
       <c r="Z672" s="1"/>
     </row>
-    <row r="673" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A673" s="8" t="s">
         <v>464</v>
       </c>
@@ -56912,7 +56904,7 @@
       <c r="A676" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="B676" s="44" t="s">
+      <c r="B676" s="16" t="s">
         <v>1609</v>
       </c>
       <c r="C676" s="25" t="s">
@@ -57041,7 +57033,7 @@
       <c r="A678" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="B678" s="44" t="s">
+      <c r="B678" s="16" t="s">
         <v>2934</v>
       </c>
       <c r="C678" s="25" t="s">
@@ -57165,7 +57157,7 @@
       </c>
       <c r="Z679" s="1"/>
     </row>
-    <row r="680" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A680" s="8" t="s">
         <v>424</v>
       </c>
@@ -57228,7 +57220,7 @@
       </c>
       <c r="Z680" s="1"/>
     </row>
-    <row r="681" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:26" ht="72" x14ac:dyDescent="0.3">
       <c r="A681" s="8" t="s">
         <v>119</v>
       </c>
@@ -57480,7 +57472,7 @@
       </c>
       <c r="Z684" s="1"/>
     </row>
-    <row r="685" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A685" s="8" t="s">
         <v>638</v>
       </c>
@@ -57606,11 +57598,11 @@
       </c>
       <c r="Z686" s="1"/>
     </row>
-    <row r="687" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A687" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="B687" s="44" t="s">
+      <c r="B687" s="16" t="s">
         <v>3033</v>
       </c>
       <c r="C687" s="25" t="s">
@@ -57671,7 +57663,7 @@
       <c r="Y687" s="1"/>
       <c r="Z687" s="1"/>
     </row>
-    <row r="688" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A688" s="8" t="s">
         <v>208</v>
       </c>
@@ -57734,7 +57726,7 @@
       </c>
       <c r="Z688" s="1"/>
     </row>
-    <row r="689" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A689" s="8" t="s">
         <v>139</v>
       </c>
@@ -57802,7 +57794,7 @@
       <c r="A690" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="B690" s="44" t="s">
+      <c r="B690" s="16" t="s">
         <v>1889</v>
       </c>
       <c r="C690" s="25" t="s">
@@ -57844,10 +57836,10 @@
       <c r="O690" s="11">
         <v>0.92320000000000002</v>
       </c>
-      <c r="P690" s="49" t="s">
+      <c r="P690" s="45" t="s">
         <v>1890</v>
       </c>
-      <c r="Q690" s="48" t="s">
+      <c r="Q690" s="18" t="s">
         <v>1890</v>
       </c>
       <c r="R690" s="13" t="s">
@@ -58053,7 +58045,7 @@
       </c>
       <c r="Z693" s="1"/>
     </row>
-    <row r="694" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A694" s="8" t="s">
         <v>470</v>
       </c>
@@ -58118,7 +58110,7 @@
       <c r="Y694" s="1"/>
       <c r="Z694" s="1"/>
     </row>
-    <row r="695" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A695" s="8" t="s">
         <v>557</v>
       </c>
@@ -58244,7 +58236,7 @@
       </c>
       <c r="Z696" s="1"/>
     </row>
-    <row r="697" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A697" s="8" t="s">
         <v>641</v>
       </c>
@@ -58370,7 +58362,7 @@
       </c>
       <c r="Z698" s="1"/>
     </row>
-    <row r="699" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A699" s="8" t="s">
         <v>149</v>
       </c>
@@ -58498,11 +58490,11 @@
       <c r="Y700" s="1"/>
       <c r="Z700" s="1"/>
     </row>
-    <row r="701" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A701" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B701" s="44" t="s">
+      <c r="B701" s="16" t="s">
         <v>1176</v>
       </c>
       <c r="C701" s="25" t="s">
@@ -58544,10 +58536,10 @@
       <c r="O701" s="11">
         <v>0.94699999999999995</v>
       </c>
-      <c r="P701" s="48" t="s">
+      <c r="P701" s="18" t="s">
         <v>1177</v>
       </c>
-      <c r="Q701" s="48" t="s">
+      <c r="Q701" s="18" t="s">
         <v>1178</v>
       </c>
       <c r="R701" s="13" t="s">
@@ -58563,7 +58555,7 @@
       <c r="Y701" s="1"/>
       <c r="Z701" s="1"/>
     </row>
-    <row r="702" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A702" s="8" t="s">
         <v>547</v>
       </c>
@@ -58819,7 +58811,7 @@
       </c>
       <c r="Z705" s="1"/>
     </row>
-    <row r="706" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A706" s="8" t="s">
         <v>678</v>
       </c>
@@ -58882,7 +58874,7 @@
       </c>
       <c r="Z706" s="1"/>
     </row>
-    <row r="707" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A707" s="8" t="s">
         <v>710</v>
       </c>
@@ -58949,7 +58941,7 @@
       <c r="A708" s="8" t="s">
         <v>379</v>
       </c>
-      <c r="B708" s="44" t="s">
+      <c r="B708" s="16" t="s">
         <v>2054</v>
       </c>
       <c r="C708" s="25" t="s">
@@ -58991,10 +58983,10 @@
       <c r="O708" s="11">
         <v>0.90969999999999995</v>
       </c>
-      <c r="P708" s="48" t="s">
+      <c r="P708" s="18" t="s">
         <v>2055</v>
       </c>
-      <c r="Q708" s="48" t="s">
+      <c r="Q708" s="18" t="s">
         <v>2055</v>
       </c>
       <c r="R708" s="13" t="s">
@@ -59014,7 +59006,7 @@
       <c r="A709" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B709" s="44" t="s">
+      <c r="B709" s="16" t="s">
         <v>809</v>
       </c>
       <c r="C709" s="25" t="s">
@@ -59138,7 +59130,7 @@
       </c>
       <c r="Z710" s="1"/>
     </row>
-    <row r="711" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A711" s="8" t="s">
         <v>679</v>
       </c>
@@ -59201,7 +59193,7 @@
       </c>
       <c r="Z711" s="1"/>
     </row>
-    <row r="712" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A712" s="8" t="s">
         <v>675</v>
       </c>
